--- a/Orçado/Orça-Seringal/BANDEIRANTES SERINGAL.xlsx
+++ b/Orçado/Orça-Seringal/BANDEIRANTES SERINGAL.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Seringal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{801CAFF4-F8F1-400A-93B7-E14F786FB45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF477CE-E7CB-456E-829A-D1AEB4C8ADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{CABEF5B8-03B8-4C74-A8CC-6028BF6D299A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$O$47</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="104">
   <si>
     <t>4.1.01.01.0001</t>
   </si>
@@ -104,124 +107,253 @@
     <t>4.1.01.21.0002</t>
   </si>
   <si>
-    <t>4.1.01.21.0003</t>
+    <t>4.1.01.21.0013</t>
+  </si>
+  <si>
+    <t>4.1.01.21.0020</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0001</t>
+  </si>
+  <si>
+    <t>4.1.01.01-CUSTO DE PESSOAL</t>
+  </si>
+  <si>
+    <t>SALARIOS E ORDENADOS</t>
+  </si>
+  <si>
+    <t>PPR</t>
+  </si>
+  <si>
+    <t>4.1.01.02-SERVICOS DE TERCEIROS</t>
+  </si>
+  <si>
+    <t>SERVICOS DE TERCEIROS PF</t>
+  </si>
+  <si>
+    <t>SERVICOS DE TERCEIROS PJ</t>
+  </si>
+  <si>
+    <t>4.1.01.03 - LOCAÇÕES</t>
+  </si>
+  <si>
+    <t>INTERNET</t>
+  </si>
+  <si>
+    <t>FRETES E CARRETOS PJ</t>
+  </si>
+  <si>
+    <t>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</t>
+  </si>
+  <si>
+    <t>PECAS, ACESSORIOS E MATERIAIS</t>
+  </si>
+  <si>
+    <t>IMPRESSOS E MATERIAIS DE EXPEDIENTE</t>
+  </si>
+  <si>
+    <t>MATERIAIS DE CONSERVACAO E LIMPEZA</t>
+  </si>
+  <si>
+    <t>COMBUSTIVEIS E LUBRIFICANTES</t>
+  </si>
+  <si>
+    <t>4.1.01.05-DEPRECIACOES, EXAUSTOES E AMORTIZACOES</t>
+  </si>
+  <si>
+    <t>DEPRECIACOES</t>
+  </si>
+  <si>
+    <t>4.1.01.06-DESPESAS DE VIAGEM</t>
+  </si>
+  <si>
+    <t>REFEICOES E ESTADIAS</t>
+  </si>
+  <si>
+    <t>OUTRAS DESPESAS DE VIAGENS</t>
+  </si>
+  <si>
+    <t>4.1.01.07-UTILIDADES E SERVICOS</t>
+  </si>
+  <si>
+    <t>TELEFONE</t>
+  </si>
+  <si>
+    <t>4.1.01.11-CUSTOS RURAIS</t>
+  </si>
+  <si>
+    <t>ALIMENTACAO ANIMAL</t>
+  </si>
+  <si>
+    <t>FERTILIZANTES</t>
+  </si>
+  <si>
+    <t>HERBICIDAS E DEFENSIVOS</t>
+  </si>
+  <si>
+    <t>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</t>
+  </si>
+  <si>
+    <t>CURSOS DE TREINAMENTO</t>
+  </si>
+  <si>
+    <t>LANCHES E REFEICOES</t>
+  </si>
+  <si>
+    <t>OUTROS CUSTOS OPERACIONAIS</t>
+  </si>
+  <si>
+    <t>4.2.01.02-RATEIO DE CUSTOS</t>
+  </si>
+  <si>
+    <t>RATEIO TRATORES LEVES</t>
+  </si>
+  <si>
+    <t>GRUPO_CONTABIL</t>
+  </si>
+  <si>
+    <t>CONTA_CONTABIL</t>
+  </si>
+  <si>
+    <t>Descrição C. Contábil</t>
+  </si>
+  <si>
+    <t>RATEIO CARRETAS TANQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS TANQUE </t>
+  </si>
+  <si>
+    <t>RATEIO CONFRATERNIZACOES E EVENTOS COM COLABORADORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO MEDICINA E SEGURANCA DO TRABALHO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO MOTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO OFICINA </t>
+  </si>
+  <si>
+    <t>RATEIO OUTROS IMPLEMENTOS</t>
+  </si>
+  <si>
+    <t>RATEIO PROGRAMA INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>RATEIO PROJETO DESENVOLVIMENTO HUMANO</t>
+  </si>
+  <si>
+    <t>RATEIO PULVERIZADORES</t>
+  </si>
+  <si>
+    <t>RATEIO REBOQUE</t>
+  </si>
+  <si>
+    <t>RATEIO RECEBIDO</t>
+  </si>
+  <si>
+    <t>RATEIO RECEBIDOS</t>
+  </si>
+  <si>
+    <t>RATEIO SEMEADORAS</t>
+  </si>
+  <si>
+    <t>RATEIO VEICULOS PESADOS</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0045</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0017</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0018</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0024</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0052</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0046</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0064</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0047</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0033</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0048</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0035</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0038</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0034</t>
+  </si>
+  <si>
+    <t>RATEIO CARRETAS AGRICOLAS</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0020</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0066</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0039</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0051</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0031</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0037</t>
+  </si>
+  <si>
+    <t>PASSAGENS</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0021</t>
+  </si>
+  <si>
+    <t>RATEIO VEICULOS MEDIOS</t>
+  </si>
+  <si>
+    <t>RATEIO PA CARREGADEIRAS</t>
+  </si>
+  <si>
+    <t>RATEIO ROCADEIRAS</t>
+  </si>
+  <si>
+    <t>RATEIO SUPERVISAO AGRICOLA OLX</t>
+  </si>
+  <si>
+    <t>RATEIO TRANSPORTE LEVE ADMINISTRACAO</t>
+  </si>
+  <si>
+    <t>RATEIO VEICULOS LEVES</t>
   </si>
   <si>
     <t>4.1.01.21.0012</t>
   </si>
   <si>
-    <t>4.1.01.21.0013</t>
-  </si>
-  <si>
-    <t>4.1.01.21.0020</t>
-  </si>
-  <si>
-    <t>4.2.01.02.0001</t>
-  </si>
-  <si>
-    <t>4.1.01.01-CUSTO DE PESSOAL</t>
-  </si>
-  <si>
-    <t>SALARIOS E ORDENADOS</t>
-  </si>
-  <si>
-    <t>PPR</t>
-  </si>
-  <si>
-    <t>4.1.01.02-SERVICOS DE TERCEIROS</t>
-  </si>
-  <si>
-    <t>SERVICOS DE TERCEIROS PF</t>
-  </si>
-  <si>
-    <t>SERVICOS DE TERCEIROS PJ</t>
-  </si>
-  <si>
-    <t>4.1.01.03 - LOCAÇÕES</t>
-  </si>
-  <si>
-    <t>INTERNET</t>
-  </si>
-  <si>
-    <t>FRETES E CARRETOS PJ</t>
-  </si>
-  <si>
-    <t>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</t>
-  </si>
-  <si>
-    <t>PECAS, ACESSORIOS E MATERIAIS</t>
-  </si>
-  <si>
-    <t>IMPRESSOS E MATERIAIS DE EXPEDIENTE</t>
-  </si>
-  <si>
-    <t>MATERIAIS DE CONSERVACAO E LIMPEZA</t>
-  </si>
-  <si>
-    <t>COMBUSTIVEIS E LUBRIFICANTES</t>
-  </si>
-  <si>
-    <t>4.1.01.05-DEPRECIACOES, EXAUSTOES E AMORTIZACOES</t>
-  </si>
-  <si>
-    <t>DEPRECIACOES</t>
-  </si>
-  <si>
-    <t>4.1.01.06-DESPESAS DE VIAGEM</t>
-  </si>
-  <si>
-    <t>REFEICOES E ESTADIAS</t>
-  </si>
-  <si>
-    <t>OUTRAS DESPESAS DE VIAGENS</t>
-  </si>
-  <si>
-    <t>4.1.01.07-UTILIDADES E SERVICOS</t>
-  </si>
-  <si>
-    <t>TELEFONE</t>
-  </si>
-  <si>
-    <t>4.1.01.11-CUSTOS RURAIS</t>
-  </si>
-  <si>
-    <t>ALIMENTACAO ANIMAL</t>
-  </si>
-  <si>
-    <t>FERTILIZANTES</t>
-  </si>
-  <si>
-    <t>HERBICIDAS E DEFENSIVOS</t>
-  </si>
-  <si>
-    <t>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</t>
-  </si>
-  <si>
-    <t>CURSOS DE TREINAMENTO</t>
-  </si>
-  <si>
-    <t>CONTRIBUICOES E DOACOES</t>
-  </si>
-  <si>
-    <t>LANCHES E REFEICOES</t>
-  </si>
-  <si>
-    <t>OUTROS CUSTOS OPERACIONAIS</t>
-  </si>
-  <si>
-    <t>4.2.01.02-RATEIO DE CUSTOS</t>
-  </si>
-  <si>
-    <t>RATEIO TRATORES LEVES</t>
-  </si>
-  <si>
-    <t>GRUPO_CONTABIL</t>
-  </si>
-  <si>
-    <t>CONTA_CONTABIL</t>
-  </si>
-  <si>
-    <t>Descrição C. Contábil</t>
+    <t>EQUIPAMENTOS DE SEGURANCA NO TRABALHO</t>
+  </si>
+  <si>
+    <t>TAXAS E ANUIDADES</t>
   </si>
 </sst>
 </file>
@@ -661,24 +793,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E02B98-8482-4B71-B8CB-F96584C0625C}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D1" s="5">
         <v>46113</v>
@@ -717,15 +849,15 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2">
         <v>724852.13227686519</v>
@@ -764,15 +896,15 @@
         <v>771261.84542417468</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -789,15 +921,15 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2">
         <v>418.47</v>
@@ -836,15 +968,15 @@
         <v>522.75599999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2">
         <v>65869.165830095662</v>
@@ -882,16 +1014,17 @@
       <c r="O5" s="2">
         <v>16768.384397353908</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -929,16 +1062,17 @@
       <c r="O6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2">
         <v>202.58</v>
@@ -976,16 +1110,17 @@
       <c r="O7" s="2">
         <v>210.89</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2">
         <v>83.694000000000017</v>
@@ -1023,16 +1158,17 @@
       <c r="O8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2">
         <v>40522.370000000003</v>
@@ -1070,16 +1206,17 @@
       <c r="O9" s="2">
         <v>7015.1382100000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2">
         <v>1737.36</v>
@@ -1117,16 +1254,17 @@
       <c r="O10" s="2">
         <v>1856.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2">
         <v>4653.9699999999993</v>
@@ -1164,16 +1302,17 @@
       <c r="O11" s="2">
         <v>4844.78</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2">
         <v>4409.8352100000002</v>
@@ -1211,16 +1350,17 @@
       <c r="O12" s="2">
         <v>4732.8253019999993</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1258,16 +1398,17 @@
       <c r="O13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2">
         <v>129522.38</v>
@@ -1305,16 +1446,17 @@
       <c r="O14" s="2">
         <v>129522.38</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15">
-        <v>0</v>
+      <c r="C15" t="s">
+        <v>93</v>
       </c>
       <c r="D15" s="2">
         <v>2281.4299999999998</v>
@@ -1352,16 +1494,17 @@
       <c r="O15" s="2">
         <v>2281.4299999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -1377,16 +1520,17 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1404,16 +1548,17 @@
       <c r="O17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2">
         <v>1798</v>
@@ -1451,16 +1596,17 @@
       <c r="O18" s="2">
         <v>1869.64</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1476,16 +1622,17 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2">
@@ -1509,16 +1656,17 @@
       <c r="O20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2">
         <v>44677.859999999993</v>
@@ -1556,290 +1704,1024 @@
       <c r="O21" s="2">
         <v>25792.219999999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2">
-        <v>8148.829999999999</v>
-      </c>
-      <c r="E22" s="2">
-        <v>7648.829999999999</v>
-      </c>
-      <c r="F22" s="2">
-        <v>7648.829999999999</v>
-      </c>
-      <c r="G22" s="2">
-        <v>7648.829999999999</v>
-      </c>
-      <c r="H22" s="2">
-        <v>7648.829999999999</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="2">
-        <v>8368.64</v>
+        <v>500</v>
       </c>
       <c r="J22" s="2">
-        <v>8368.64</v>
+        <v>500</v>
       </c>
       <c r="K22" s="2">
-        <v>8368.64</v>
+        <v>500</v>
       </c>
       <c r="L22" s="2">
-        <v>8368.64</v>
+        <v>500</v>
       </c>
       <c r="M22" s="2">
-        <v>8461.76</v>
+        <v>500</v>
       </c>
       <c r="N22" s="2">
-        <v>8461.76</v>
+        <v>500</v>
       </c>
       <c r="O22" s="2">
-        <v>8741.1200000000008</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
-        <v>53</v>
-      </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>37427.519550000005</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>37427.519550000005</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>38805.624795000003</v>
       </c>
       <c r="G23" s="2">
-        <v>0</v>
+        <v>38805.624795000003</v>
       </c>
       <c r="H23" s="2">
-        <v>0</v>
+        <v>38805.624795000003</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>38237.184999999998</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>38237.184999999998</v>
       </c>
       <c r="K23" s="2">
-        <v>0</v>
+        <v>38237.184999999998</v>
       </c>
       <c r="L23" s="2">
-        <v>0</v>
+        <v>38237.184999999998</v>
       </c>
       <c r="M23" s="2">
-        <v>0</v>
+        <v>37011.750544999995</v>
       </c>
       <c r="N23" s="2">
-        <v>0</v>
+        <v>26969.437990999999</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>41635.758034999999</v>
+      </c>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1359.45</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1359.45</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1359.45</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1359.45</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1359.45</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1399.32</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1399.32</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1399.32</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1399.32</v>
+      </c>
+      <c r="M24" s="2">
+        <v>1415.8799999999999</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1415.8799999999999</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1465.56</v>
+      </c>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5289.37</v>
+      </c>
+      <c r="E25" s="2">
+        <v>931.21</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1746.49</v>
+      </c>
+      <c r="G25" s="2">
+        <v>965.42</v>
+      </c>
+      <c r="H25" s="2">
+        <v>759.06</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="2">
+        <v>254.96</v>
+      </c>
+      <c r="E26" s="2">
+        <v>254.96</v>
+      </c>
+      <c r="F26" s="2">
+        <v>254.96</v>
+      </c>
+      <c r="G26" s="2">
+        <v>254.96</v>
+      </c>
+      <c r="H26" s="2">
+        <v>254.96</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="2">
+        <v>846.47051999999996</v>
+      </c>
+      <c r="E28" s="2">
+        <v>883.86480000000006</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4724.7299999999996</v>
+      </c>
+      <c r="G28" s="2">
+        <v>600.20999999999992</v>
+      </c>
+      <c r="H28" s="2">
+        <v>200.07</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5995.26</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5995.26</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6265.0467000000008</v>
+      </c>
+      <c r="G29" s="2">
+        <v>6265.0467000000008</v>
+      </c>
+      <c r="H29" s="2">
+        <v>6265.0467000000008</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5685.6</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5685.6</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5941.4519999999993</v>
+      </c>
+      <c r="G30" s="2">
+        <v>5941.4519999999993</v>
+      </c>
+      <c r="H30" s="2">
+        <v>5941.4519999999993</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="2">
+        <v>164</v>
+      </c>
+      <c r="E31" s="2">
+        <v>164</v>
+      </c>
+      <c r="F31" s="2">
+        <v>164</v>
+      </c>
+      <c r="G31" s="2">
+        <v>164</v>
+      </c>
+      <c r="H31" s="2">
+        <v>164</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="2">
+        <v>6321.84</v>
+      </c>
+      <c r="E32" s="2">
+        <v>6321.84</v>
+      </c>
+      <c r="F32" s="2">
+        <v>6321.84</v>
+      </c>
+      <c r="G32" s="2">
+        <v>6321.84</v>
+      </c>
+      <c r="H32" s="2">
+        <v>6321.84</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="E33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="G33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="H33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="2">
+        <v>855</v>
+      </c>
+      <c r="E34" s="2">
+        <v>855</v>
+      </c>
+      <c r="F34" s="2">
+        <v>855</v>
+      </c>
+      <c r="G34" s="2">
+        <v>855</v>
+      </c>
+      <c r="H34" s="2">
+        <v>855</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1150.8300000000002</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1150.8300000000002</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1150.8300000000002</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1150.8300000000002</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1150.8300000000002</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="2">
+        <v>209.73</v>
+      </c>
+      <c r="E36" s="2">
+        <v>209.73</v>
+      </c>
+      <c r="F36" s="2">
+        <v>209.73</v>
+      </c>
+      <c r="G36" s="2">
+        <v>209.73</v>
+      </c>
+      <c r="H36" s="2">
+        <v>209.73</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>170801.76631447289</v>
+      </c>
+      <c r="J38" s="2">
+        <v>167306.20096685286</v>
+      </c>
+      <c r="K38" s="2">
+        <v>236255.23268634288</v>
+      </c>
+      <c r="L38" s="2">
+        <v>200873.61885887288</v>
+      </c>
+      <c r="M38" s="2">
+        <v>152428.51381348426</v>
+      </c>
+      <c r="N38" s="2">
+        <v>153117.95453740825</v>
+      </c>
+      <c r="O38" s="2">
+        <v>161352.89919790823</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4300</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1786.73</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>105.83</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1702</v>
+      </c>
+      <c r="E41" s="2">
+        <v>461</v>
+      </c>
+      <c r="F41" s="2">
+        <v>660</v>
+      </c>
+      <c r="G41" s="2">
+        <v>461</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="2">
+        <v>25581.343084686112</v>
+      </c>
+      <c r="E42" s="2">
+        <v>26742.285288644114</v>
+      </c>
+      <c r="F42" s="2">
+        <v>27218.812191246943</v>
+      </c>
+      <c r="G42" s="2">
+        <v>39136.151451246944</v>
+      </c>
+      <c r="H42" s="2">
+        <v>27888.255351246949</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1396</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1396</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1396</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1396</v>
+      </c>
+      <c r="H43" s="2">
+        <v>1396</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="2">
-        <v>6234.6685499999994</v>
-      </c>
-      <c r="E24" s="2">
-        <v>6234.6685499999994</v>
-      </c>
-      <c r="F24" s="2">
-        <v>6234.6685499999994</v>
-      </c>
-      <c r="G24" s="2">
-        <v>6234.6685499999994</v>
-      </c>
-      <c r="H24" s="2">
-        <v>6234.6685499999994</v>
-      </c>
-      <c r="I24" s="2">
-        <v>6138.08</v>
-      </c>
-      <c r="J24" s="2">
-        <v>6138.08</v>
-      </c>
-      <c r="K24" s="2">
-        <v>6138.08</v>
-      </c>
-      <c r="L24" s="2">
-        <v>6138.08</v>
-      </c>
-      <c r="M24" s="2">
-        <v>3232.67976</v>
-      </c>
-      <c r="N24" s="2">
-        <v>6465.35952</v>
-      </c>
-      <c r="O24" s="2">
-        <v>6692.2142400000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="2">
-        <v>32262.851000000002</v>
-      </c>
-      <c r="E25" s="2">
-        <v>31192.851000000002</v>
-      </c>
-      <c r="F25" s="2">
-        <v>32570.956245000001</v>
-      </c>
-      <c r="G25" s="2">
-        <v>32570.956245000001</v>
-      </c>
-      <c r="H25" s="2">
-        <v>33570.956245000001</v>
-      </c>
-      <c r="I25" s="2">
-        <v>32099.105</v>
-      </c>
-      <c r="J25" s="2">
-        <v>32099.105</v>
-      </c>
-      <c r="K25" s="2">
-        <v>33099.104999999996</v>
-      </c>
-      <c r="L25" s="2">
-        <v>33099.104999999996</v>
-      </c>
-      <c r="M25" s="2">
-        <v>33779.070784999996</v>
-      </c>
-      <c r="N25" s="2">
-        <v>21504.078471000001</v>
-      </c>
-      <c r="O25" s="2">
-        <v>34943.543794999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1359.45</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1359.45</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1359.45</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1359.45</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1359.45</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1399.32</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1399.32</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1399.32</v>
-      </c>
-      <c r="L26" s="2">
-        <v>1399.32</v>
-      </c>
-      <c r="M26" s="2">
-        <v>1415.8799999999999</v>
-      </c>
-      <c r="N26" s="2">
-        <v>1415.8799999999999</v>
-      </c>
-      <c r="O26" s="2">
-        <v>1465.56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="2">
-        <v>152157.37796468611</v>
-      </c>
-      <c r="E27" s="2">
-        <v>156428.74296864413</v>
-      </c>
-      <c r="F27" s="2">
-        <v>167911.43057124695</v>
-      </c>
-      <c r="G27" s="2">
-        <v>173549.33635124695</v>
-      </c>
-      <c r="H27" s="2">
-        <v>168786.89777124696</v>
-      </c>
-      <c r="I27" s="2">
-        <v>170801.76631447289</v>
-      </c>
-      <c r="J27" s="2">
-        <v>167306.20096685286</v>
-      </c>
-      <c r="K27" s="2">
-        <v>236255.23268634288</v>
-      </c>
-      <c r="L27" s="2">
-        <v>200873.61885887288</v>
-      </c>
-      <c r="M27" s="2">
-        <v>152428.51381348426</v>
-      </c>
-      <c r="N27" s="2">
-        <v>153117.95453740825</v>
-      </c>
-      <c r="O27" s="2">
-        <v>161352.89919790823</v>
-      </c>
+      <c r="D44" s="2">
+        <v>22191.984359999999</v>
+      </c>
+      <c r="E44" s="2">
+        <v>26564.172880000002</v>
+      </c>
+      <c r="F44" s="2">
+        <v>32065.714380000001</v>
+      </c>
+      <c r="G44" s="2">
+        <v>32677.600899999998</v>
+      </c>
+      <c r="H44" s="2">
+        <v>40124.728419999999</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="2">
+        <v>8063.24</v>
+      </c>
+      <c r="E45" s="2">
+        <v>8063.24</v>
+      </c>
+      <c r="F45" s="2">
+        <v>8063.24</v>
+      </c>
+      <c r="G45" s="2">
+        <v>8063.24</v>
+      </c>
+      <c r="H45" s="2">
+        <v>8063.24</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="2">
+        <v>58602.34</v>
+      </c>
+      <c r="E46" s="2">
+        <v>58602.34</v>
+      </c>
+      <c r="F46" s="2">
+        <v>61239.445299999999</v>
+      </c>
+      <c r="G46" s="2">
+        <v>61239.445299999999</v>
+      </c>
+      <c r="H46" s="2">
+        <v>61239.445299999999</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1547.41</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1547.41</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1547.41</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1547.41</v>
+      </c>
+      <c r="H47" s="2">
+        <v>1547.41</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="2">
+        <v>7648.829999999999</v>
+      </c>
+      <c r="E48" s="2">
+        <v>7648.829999999999</v>
+      </c>
+      <c r="F48" s="2">
+        <v>7648.829999999999</v>
+      </c>
+      <c r="G48" s="2">
+        <v>7648.829999999999</v>
+      </c>
+      <c r="H48" s="2">
+        <v>7648.829999999999</v>
+      </c>
+      <c r="I48" s="2">
+        <v>7868.64</v>
+      </c>
+      <c r="J48" s="2">
+        <v>7868.64</v>
+      </c>
+      <c r="K48" s="2">
+        <v>7868.64</v>
+      </c>
+      <c r="L48" s="2">
+        <v>7868.64</v>
+      </c>
+      <c r="M48" s="2">
+        <v>7961.76</v>
+      </c>
+      <c r="N48" s="2">
+        <v>7961.76</v>
+      </c>
+      <c r="O48" s="2">
+        <v>8241.1200000000008</v>
+      </c>
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="2">
+        <v>1070</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O47" xr:uid="{D6E02B98-8482-4B71-B8CB-F96584C0625C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>